--- a/backend/Invoice_239_20251020.xlsx
+++ b/backend/Invoice_239_20251020.xlsx
@@ -80,7 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -467,19 +469,19 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,7 +504,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-07-23</t>
         </is>
       </c>
     </row>
@@ -611,7 +613,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Bus Fare</t>
+          <t>Fare</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -696,8 +698,8 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-07-23</t>
         </is>
       </c>
     </row>
